--- a/data/trans_bre/IP18_E_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18_E_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 14,52</t>
+          <t>-3,07; 14,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 10,75</t>
+          <t>-4,49; 11,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 11,21</t>
+          <t>-4,25; 11,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-54,64; -8,75</t>
+          <t>-54,21; -9,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 18,99</t>
+          <t>-3,59; 18,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 12,97</t>
+          <t>-4,96; 14,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 14,15</t>
+          <t>-4,81; 14,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-57,15; -10,12</t>
+          <t>-58,13; -10,57</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 5,35</t>
+          <t>-10,03; 5,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 2,2</t>
+          <t>-11,98; 3,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 5,68</t>
+          <t>-9,98; 5,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,75; 4,65</t>
+          <t>-58,09; 3,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 6,11</t>
+          <t>-10,37; 6,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 2,31</t>
+          <t>-12,79; 3,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 6,58</t>
+          <t>-10,77; 6,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,9; 5,99</t>
+          <t>-67,55; 3,88</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 7,83</t>
+          <t>-4,32; 7,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 3,29</t>
+          <t>-5,13; 3,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 8,36</t>
+          <t>-5,1; 8,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,18</t>
+          <t>0,0; 27,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 8,66</t>
+          <t>-4,37; 8,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 3,47</t>
+          <t>-5,18; 3,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 9,41</t>
+          <t>-5,2; 10,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,22</t>
+          <t>0,0; 37,02</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 2,35</t>
+          <t>-5,13; 2,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,89</t>
+          <t>-2,34; 4,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 0,82</t>
+          <t>-4,77; 0,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 9,93</t>
+          <t>-7,18; 9,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 2,48</t>
+          <t>-5,25; 2,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 5,29</t>
+          <t>-2,41; 4,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,86</t>
+          <t>-4,9; 0,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 11,15</t>
+          <t>-7,3; 11,36</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 3,05</t>
+          <t>-2,72; 2,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,79</t>
+          <t>-2,69; 1,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,82</t>
+          <t>-1,82; 2,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 0,0</t>
+          <t>-17,41; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 3,15</t>
+          <t>-2,74; 3,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,83</t>
+          <t>-2,72; 1,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,91</t>
+          <t>-1,83; 2,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 0,0</t>
+          <t>-17,41; 0,0</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 7,69</t>
+          <t>-4,66; 7,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 1,31</t>
+          <t>-8,45; 1,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 1,42</t>
+          <t>-8,65; 1,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 11,58</t>
+          <t>-19,62; 11,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 8,55</t>
+          <t>-4,83; 8,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 1,34</t>
+          <t>-8,51; 1,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 1,41</t>
+          <t>-8,76; 1,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 13,16</t>
+          <t>-20,4; 12,68</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,41</t>
+          <t>-2,11; 2,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,59</t>
+          <t>-2,34; 1,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,94</t>
+          <t>-2,58; 1,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,13; -3,35</t>
+          <t>-20,32; -2,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,63</t>
+          <t>-2,25; 2,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,7</t>
+          <t>-2,44; 1,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 2,05</t>
+          <t>-2,7; 1,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-21,08; -3,65</t>
+          <t>-21,81; -3,13</t>
         </is>
       </c>
     </row>
